--- a/order_forms/035_itin_preparation_service_form--order_forms.xlsx
+++ b/order_forms/035_itin_preparation_service_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1038,17 +1038,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date_of_birth_control_choices</t>
+          <t>tin_status_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>02/15/1999</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>02/15/1999</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>invalid</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Invalid</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>invalid</t>
+          <t>not_active</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Invalid</t>
+          <t>Not Active</t>
         </is>
       </c>
     </row>
@@ -1094,29 +1094,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_active</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Not Active</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tin_status_choices</t>
+          <t>reason_for_application_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>taxpayer_identification_number</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Taxpayer Identification Number</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>taxpayer_identification_number</t>
+          <t>w-2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Taxpayer Identification Number</t>
+          <t>W-2</t>
         </is>
       </c>
     </row>
@@ -1145,19 +1145,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>w-2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>reason_for_application_choices</t>
+          <t>reason_for_inactivation_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>taxpayer_identification_number</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Taxpayer Identification Number</t>
         </is>
       </c>
     </row>
@@ -1196,27 +1196,10 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>taxpayer_identification_number</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
-        <is>
-          <t>Taxpayer Identification Number</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>reason_for_inactivation_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
         <is>
           <t>None</t>
         </is>
